--- a/affiliate_data/rocket_curated.xlsx
+++ b/affiliate_data/rocket_curated.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1733,6 +1733,106 @@
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>48900.00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>39900.00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>34900.00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>26900.00</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/affiliate_data/rocket_curated.xlsx
+++ b/affiliate_data/rocket_curated.xlsx
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/affiliate_data/rocket_curated.xlsx
+++ b/affiliate_data/rocket_curated.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1833,6 +1833,716 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2250.00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ขายได้ 2พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/55250250242</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4100.00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ขายได้ 410 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/19781507501</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBAKIWf</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1319.00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ขายได้ 8พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/28167956378</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AOkJG7XeU</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 17/17 Air/17 Pro/17 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-me464fn2gzy9c4.webp</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>690.00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ขายได้ 2พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/41766852090</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pltueeZSk</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1798.00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ขายได้ 10พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/25527756989</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1AVOUsEit</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rubber Killer - JOURNEY LOGO T-SHIRT (เสื้อยืดคอกลม)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lu0rwfi2o9ht0d.webp</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>950.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ขายได้ 1พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/24223838973</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40ge9qm9Up</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4730.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ขายได้ 915 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/24406480605</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1955.00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ขายได้ 6พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/45704393767</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>9490.00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ขายได้ 10พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/18478170373</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50ZBLhh7GG</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>875.00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ขายได้ 3พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/22549935932</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>634.00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ขายได้ 6พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/42006405121</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNIQ Combat เคสไอโฟน สำหรับ iPhone 18 Pro/18 Pro Max (วงแหวน MagClick™) เคสโทรศัพท์</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-msm7y6m7hs7409.webp</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ขายได้ 165 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/49066280712</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAHHVDfOkK</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>14290.00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ขายได้ 100พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/13181175093</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1287.00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ขายได้ 15 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/52809274489</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VcukpE2bD</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>🔥พร้อมส่ง🔥 เสื้อ Guns N' Roses Thailand Bankok (2017) Tee - Black (สีดำ) by XSHT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-ly6pmx1kzfl554.webp</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>595.00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ขายได้ 201 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/28256346778</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBJt9y0</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2107.00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ขายได้ 128 ชิ้น</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/25275966912</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
